--- a/Consolidado de observaciones SI EAA MOD 0.xlsx
+++ b/Consolidado de observaciones SI EAA MOD 0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Desarrollos\2025\Automatizaciones\Sis_HS_IETS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC65218-FAC3-4842-8962-E74B9B8BB3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C69C527-7446-413E-B408-F71ECCDD6009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName name="Z_FFCB727A_5934_44AA_9A00_23745F16FD55_.wvu.FilterData" localSheetId="1" hidden="1">'OBSERVACIONES SI EAA'!$A$1:$K$7</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <customWorkbookViews>
     <customWorkbookView name="Tabla2 filter view" guid="{FFCB727A-5934-44AA-9A00-23745F16FD55}" maximized="1" windowWidth="0" windowHeight="0" activeSheetId="0"/>
   </customWorkbookViews>
@@ -45,6 +45,7 @@
             <sz val="11"/>
             <color theme="1"/>
             <rFont val="Calibri"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t>======
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="97">
   <si>
     <t>N°</t>
   </si>
@@ -362,6 +363,45 @@
   </si>
   <si>
     <t>Ver OBS-001. Prioridad oficial cargada al 27-10-2026: 53 alta, 4 media, 19 «revisar» y 17 sin asignar (columna Observaciones). Para confirmarla, el Catálogo de fuentes muestra junto a cada fuente la «Prioridad sugerida» por la relevancia de sus señales y el botón «Aplicar». Acción del equipo técnico: revisar las 36 en «revisar» o sin asignar y reflejar la decisión en el Excel institucional. Guía §4.4 y §8.9.</t>
+  </si>
+  <si>
+    <t>Especificación técnica</t>
+  </si>
+  <si>
+    <t>CÓMO SE CUMPLE
+1) Conectores por API (módulo Vigilancia): ClinicalTrials.gov (API v2 en JSON) filtra por defecto estudios en Fase II, III y IV (ajustable por fuente); WHO ICTRP (no tiene API pública estable: lee el espejo o el lote que se configure en la fuente); FDA por openFDA (aprobaciones de medicamentos Drugs@FDA y dispositivos 510(k) y PMA); EMA (reporte oficial «Medicines output» en JSON, con el RSS de noticias como respaldo); además Health Canada, CTIS (UE), PubMed y PCORI. Las fuentes sin API (p. ej. FDA Breakthrough Devices, EuroScan y las agencias de ETS) se leen desde su página web con recorrido guiado y lectura con IA.
+2) Tareas programadas (cron): un proceso del servidor revisa la cola cada 20 segundos y encola cada fuente cuando vence su frecuencia, tomada de la matriz (diaria 24 h, semanal 168 h, mensual 720 h, etc.). En Configuración › Tareas programadas se fija cada cuántas horas se revisan las fuentes vencidas y se puede «Correr ahora». Si una fuente falla se reintenta hasta 3 veces y no detiene a las demás.
+3) Fuentes y rutas confirmadas: las define la matriz institucional «FUENTES DE INFORMACIÓN PROACTIVA EH» (93 filas → 97 fuentes y 128 URL de consulta SI EAA), que el sistema carga solo al iniciar. Cada fuente y sus URL se ven en Catálogo de fuentes › Ficha.
+DÓNDE VERLO: Vigilancia (cola y resultados), Catálogo de fuentes, Configuración › Tareas programadas.
+CÓMO PROBARLO: Catálogo de fuentes › ClinicalTrials.gov › «Ingerir» → aviso «Ingesta: X nuevas de Y» → las señales aparecen en la Bandeja de entrada con su fase.
+Guía de usuario §8, §9, §25.4 y §30.</t>
+  </si>
+  <si>
+    <t>CÓMO SE CUMPLE
+1) Portal público en la ruta /postular: no requiere cuenta. Autenticación ligera contra robots: reCAPTCHA (si está activo; si no, tope de envíos por IP) y un campo trampa oculto.
+2) Campos obligatorios validados en el servidor (no se puede enviar sin ellos): nombre comercial y DCI/principio activo; mecanismo de acción o principio de funcionamiento; fabricante o desarrollador; indicación/patología diana; fase de desarrollo actual; al menos un enlace a evidencia científica (http/https); nombre y correo de quien postula; firma de la declaración de conflictos de interés (si declara un conflicto, debe describirlo en al menos 20 caracteres). La organización es opcional.
+3) Moderación: la postulación llega con estado «recibida» al módulo Postulaciones. El evaluador la acepta (entra a la Bandeja de entrada con canal «reactiva») o la rechaza escribiendo el motivo. Todo queda en la bitácora de auditoría.
+DÓNDE VERLO: /postular (externo) y menú Postulaciones (interno).
+CÓMO PROBARLO: enviar una postulación dejando un campo obligatorio vacío (el sistema la rechaza indicando el campo); enviarla completa → aparece en Postulaciones → «Aceptar» → aparece en la Bandeja de entrada con canal «Postulación reactiva».
+Guía de usuario §11 y §26.</t>
+  </si>
+  <si>
+    <t>CÓMO SE CUMPLE
+1) Toda señal, proactiva o reactiva, se guarda en la tabla de acopio de tecnologías con el estado «capturada_no_asignada» (Capturada / No asignada) hasta que se asigna a un ciclo. Nada se pierde: lo que se descarta queda marcado, no se borra.
+2) Metadatos de auditoría de cada registro: fecha y hora exacta de captura (captured_at, con zona horaria); fuente de origen (enlazada al Catálogo de fuentes) y canal (source_channel: «proactiva» = vigilancia, «reactiva» = postulación); usuario o proceso que ejecutó la ingesta (captured_by: quien lanzó la vigilancia o el proceso/conector programado). Además guarda el registro original tal como llegó de la fuente (botón «Ver JSON original») y la URL exacta de captura.
+3) La bitácora de auditoría registra cada alta y cada cambio con usuario, fecha y operación.
+DÓNDE VERLO: Bandeja de entrada (fuente, fecha y canal en cada fila; «Clasificar» › «Ver JSON original» y «↗ Abrir la fuente original») y Bitácora de auditoría.
+CÓMO PROBARLO: «Ingerir» una fuente → la señal nueva aparece en la Bandeja con fecha y hora, fuente y canal «proactiva»; aceptar una postulación → aparece con canal «reactiva».
+Guía de usuario §10, §11 y §23.</t>
+  </si>
+  <si>
+    <t>CÓMO SE CUMPLE
+1) Bandeja de entrada (menú «Bandeja de entrada»): lista las señales sin ciclo con nombre, datos de producto (forma, concentración, vía, marca, modelo), fuente, fecha de captura, canal, puntaje de cribado y la etiqueta «En N fuentes» cuando otra fuente reporta la misma tecnología.
+2) Filtros: texto (nombre, DCI o resumen), fuente, canal (proactiva/reactiva), rango de fechas de captura «Desde / Hasta» (agregado el 29-10-2026, en hora de Colombia) y «Solo detectadas en varias fuentes». Indicadores arriba: sin asignar, sin clúster/tipología, en varias fuentes y listas para asignar.
+3) Pre-visualización: «Clasificar» abre la ficha con el resumen, el enlace a la fuente original, el JSON original, los datos de producto y la sugerencia de clasificación (IA o reglas), que el evaluador confirma o corrige.
+4) Transferencia por lotes al Módulo 1: se marcan varias filas y «Asignar al ciclo» las pasa al ciclo seleccionado en el encabezado. Regla: cada señal debe tener clúster y tipología; las que no cumplen se informan sin bloquear a las demás. Permiso «Asignar al ciclo» (evaluadores y superadministrador).
+CÓMO PROBARLO: filtrar por una fuente y un rango de fechas → clasificar 2 o 3 señales → marcarlas → «Asignar al ciclo» → aparecen en Filtrado y depuración del ciclo.
+Guía de usuario §10.</t>
   </si>
 </sst>
 </file>
@@ -382,17 +422,20 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -480,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -517,14 +560,23 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -532,23 +584,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -622,15 +687,15 @@
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="PRUEBAS FUNCIONALES SI EAA-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="headerRow" dxfId="6"/>
-      <tableStyleElement type="firstRowStripe" dxfId="5"/>
-      <tableStyleElement type="secondRowStripe" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="firstRowStripe" dxfId="6"/>
+      <tableStyleElement type="secondRowStripe" dxfId="5"/>
     </tableStyle>
     <tableStyle name="OBSERVACIONES SI EAA-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
-      <tableStyleElement type="headerRow" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -645,8 +710,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:G6">
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:H6">
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="N°"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Modulo"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Descripción"/>
@@ -654,6 +719,7 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Validación Equipo Técnico"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Observaciones"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Seguimiento"/>
+    <tableColumn id="8" xr3:uid="{5C9DE1FD-1DEF-48AA-8761-27E16E040A0A}" name="Especificación técnica" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="PRUEBAS FUNCIONALES SI EAA-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -879,16 +945,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="85.6640625" customWidth="1"/>
     <col min="4" max="4" width="23.33203125" customWidth="1"/>
     <col min="5" max="5" width="25" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="110.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -910,8 +977,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="H1" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
@@ -921,8 +991,11 @@
       <c r="C2" s="11" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="H2" s="25" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
@@ -936,8 +1009,11 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="H3" s="25" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -951,8 +1027,11 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="H4" s="25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
@@ -966,8 +1045,11 @@
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="H5" s="25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1337,191 +1419,191 @@
       <c r="C9" s="10"/>
     </row>
     <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15" t="s">
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="16"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="24"/>
     </row>
     <row r="11" spans="1:26" ht="171" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="17" t="s">
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="18"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="17"/>
     </row>
     <row r="12" spans="1:26" ht="126" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="17" t="s">
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="18"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="17"/>
     </row>
     <row r="13" spans="1:26" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="17" t="s">
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="18"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="17"/>
     </row>
     <row r="14" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="17" t="s">
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="18"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="17"/>
     </row>
     <row r="15" spans="1:26" ht="141" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="17" t="s">
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="18"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17"/>
     </row>
     <row r="16" spans="1:26" ht="96" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="17" t="s">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="18"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="17"/>
     </row>
     <row r="17" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="17" t="s">
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="18"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="17"/>
     </row>
     <row r="18" spans="1:11" ht="126" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="17" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="18"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="17"/>
     </row>
     <row r="19" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="17" t="s">
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="18"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="17"/>
     </row>
     <row r="20" spans="1:11" ht="81" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23" t="s">
+      <c r="A20" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="17" t="s">
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
-      <c r="K20" s="18"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="17"/>
     </row>
     <row r="21" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="10"/>
@@ -5447,7 +5529,7 @@
   <customSheetViews>
     <customSheetView guid="{FFCB727A-5934-44AA-9A00-23745F16FD55}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="A1:K7" xr:uid="{34D2E9F4-2A79-4118-951B-2949F9B93D8F}"/>
+      <autoFilter ref="A1:K7" xr:uid="{AE0992B6-0B10-4709-84DF-0F9A43EFD593}"/>
       <extLst>
         <ext uri="GoogleSheetsCustomDataVersion1">
           <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" filterViewId="866626896"/>
@@ -5456,12 +5538,14 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="22">
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="H14:K14"/>
     <mergeCell ref="H15:K15"/>
     <mergeCell ref="H16:K16"/>
@@ -5470,14 +5554,12 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="H20:K20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
